--- a/NAKS/НАКС_парсинг/naks_главное.xlsx
+++ b/NAKS/НАКС_парсинг/naks_главное.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,51 +486,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Власов Юрий Николаевич</t>
+          <t>Долгоносов Максим Иванович</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3BBF</t>
+          <t>355X</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ООО «ВЕК», Екатеринбург</t>
+          <t>ООО "СК Авторитет", Санкт-Петербург</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Сварщик</t>
+          <t>Сварщик 4 разряда</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ТОР-5АЦ-I-08492</t>
+          <t>СЗР-13АЦ-I-01995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>МР-1ГАЦ</t>
+          <t>СЗР-13АЦ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>03.04.2025</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>12.11.2024</t>
-        </is>
-      </c>
+          <t>03.04.2027</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>РД</t>
@@ -538,106 +534,110 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>КО, ОХНВП, СК  подробнее</t>
+          <t>КО, СК  подробнее</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Власов Юрий Николаевич</t>
+          <t>Долгоносов Максим Иванович</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3BBF</t>
+          <t>355X</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ООО «ВЕК», Тюмень</t>
+          <t>ООО "СТРОЙ ГАРАНТ", Тосно</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Сварщик 6 разряда</t>
+          <t>Сварщик 4 разряда</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>СУР-10АЦ-I-02118</t>
+          <t>СЗР-6АЦ-I-15527</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>СУР-10АЦ</t>
+          <t>СЗР-6АЦ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.06.2023</t>
+          <t>20.09.2024</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.06.2025</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>РАД</t>
+          <t>РД</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>НГДО, ОХНВП, СК  подробнее</t>
+          <t>КО  подробнее</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Власов Юрий Николаевич</t>
+          <t>Долгоносов Максим Иванович</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3BBF</t>
+          <t>355X</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ООО"ВЕК", Тюмень</t>
+          <t>ООО "СК Авторитет", Санкт-Петербург</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Сварщик 6-го разряда</t>
+          <t>Сварщик 4-го разряда</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ТОР-5АЦ-I-08492</t>
+          <t>СЗР-1ГАЦ-I-37388</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ТОР-5АЦ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>СЗР-1ГАЦ</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>39АП</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12.11.2021</t>
+          <t>04.04.2019</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>04.04.2021</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -648,571 +648,62 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>КО, ОХНВП, СК  подробнее</t>
+          <t>КО, СК  подробнее</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Власов Юрий Николаевич</t>
+          <t>Долгоносов Максим Иванович</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3BBF</t>
+          <t>355X</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ООО «ВЕК», Тюмень</t>
+          <t>ООО "Строй Плюс", г. Санкт-Петербург</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Сварщик 6-го разряда</t>
+          <t>Сварщик 4-го разряда</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>СУР-10АЦ-I-01919</t>
+          <t>СЗР-6АЦ-I-04389</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>СУР-10АЦ</t>
+          <t>СЗР-6АЦ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15.03.2021</t>
+          <t>28.07.2015</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.03.2023</t>
+          <t>28.07.2017</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>РАД</t>
+          <t>РД</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>КО, ОХНВП, СК  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", г. Москва</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-07683</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>В1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>СУР-24АЦ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>24.09.2019</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>15.04.2021</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>РАД</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ОХНВП  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", г. Москва</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-07682</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>В2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>СУР-24АЦ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>24.09.2019</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>15.04.2021</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>РД</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ОХНВП  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", Москва</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-07682</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15.04.2019</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>15.04.2021</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>РД</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>КО, ОХНВП, СК  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", Тюмень</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-07683</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15.04.2019</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>15.04.2021</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>РАД</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>КО, ОХНВП, СК  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", Москва</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-07682</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>В1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15.04.2019</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15.04.2021</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>РД</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>СК  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", г. Москва</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-06116</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>02.02.2017</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>02.02.2019</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>РАД</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>НГДО, ОХНВП, СК  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ООО "ВелесстройМонтаж", г. Москва</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-06134</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>02.02.2017</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>02.02.2019</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>РД</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>НГДО, ОХНВП, СК  подробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ООО "Велесстрой", г. Белград</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-04326</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25.08.2015</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>25.08.2017</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>РАД</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>НГДО 
-ТНподробнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Власов Юрий Николаевич</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3BBF</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ООО "Велесстрой", г. Белград</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Сварщик 6-го разряда</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ-I-04327</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>СУР-17АЦ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25.08.2015</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>25.08.2017</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>РД</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>НГДО 
-ТНподробнее</t>
+          <t>КО, СК  подробнее</t>
         </is>
       </c>
     </row>
